--- a/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
@@ -1559,19 +1559,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1669,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1749,7 +1749,7 @@
         <v>207.9471</v>
       </c>
       <c r="P4" t="n">
-        <v>5.926492350000001</v>
+        <v>5.92649235</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.131628207280301e-14</v>
+        <v>3.552713678800501e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1823,10 +1823,10 @@
         <v>127.3302692500002</v>
       </c>
       <c r="N5" t="n">
-        <v>346.0372000000001</v>
+        <v>346.0372</v>
       </c>
       <c r="O5" t="n">
-        <v>346.0372000000001</v>
+        <v>346.0372</v>
       </c>
       <c r="P5" t="n">
         <v>4.152446400000001</v>
@@ -1841,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>73.1545591166668</v>
+        <v>73.15455911666682</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-7.105427357601002e-14</v>
+        <v>-1.56319401867222e-13</v>
       </c>
     </row>
     <row r="6">
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-1.13686837721616e-13</v>
       </c>
     </row>
     <row r="7">
@@ -1962,7 +1962,7 @@
         <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -4875,7 +4875,7 @@
         <v>30.5031</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L40" t="n">
         <v>64.43003738333343</v>
@@ -4946,7 +4946,7 @@
         <v>30.5031</v>
       </c>
       <c r="K41" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L41" t="n">
         <v>73.73376685000011</v>
@@ -5017,7 +5017,7 @@
         <v>30.5031</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L42" t="n">
         <v>83.03749631666679</v>
@@ -5088,7 +5088,7 @@
         <v>30.5031</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L43" t="n">
         <v>92.34122578333347</v>
@@ -5159,7 +5159,7 @@
         <v>30.5031</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L44" t="n">
         <v>101.6449552500002</v>
@@ -5230,7 +5230,7 @@
         <v>30.5031</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L45" t="n">
         <v>110.9486847166668</v>
@@ -5301,7 +5301,7 @@
         <v>30.5031</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L46" t="n">
         <v>120.2524141833335</v>
@@ -5372,7 +5372,7 @@
         <v>30.5031</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L47" t="n">
         <v>129.5561436500002</v>
@@ -5443,7 +5443,7 @@
         <v>30.5031</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L48" t="n">
         <v>138.8598731166669</v>
@@ -5514,7 +5514,7 @@
         <v>30.5031</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3660372000000001</v>
+        <v>0.3660372</v>
       </c>
       <c r="L49" t="n">
         <v>148.1636025833336</v>
@@ -5585,7 +5585,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K50" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L50" t="n">
         <v>161.2939960166669</v>
@@ -5656,7 +5656,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L51" t="n">
         <v>168.5910561166669</v>
@@ -5727,7 +5727,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L52" t="n">
         <v>175.8881162166669</v>
@@ -5798,7 +5798,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L53" t="n">
         <v>183.1851763166669</v>
@@ -5869,7 +5869,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K54" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L54" t="n">
         <v>190.482236416667</v>
@@ -5940,7 +5940,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L55" t="n">
         <v>197.779296516667</v>
@@ -6011,7 +6011,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K56" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L56" t="n">
         <v>205.076356616667</v>
@@ -6082,7 +6082,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L57" t="n">
         <v>212.373416716667</v>
@@ -6153,7 +6153,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L58" t="n">
         <v>219.670476816667</v>
@@ -6224,7 +6224,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L59" t="n">
         <v>226.967536916667</v>
@@ -6295,7 +6295,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L60" t="n">
         <v>234.264597016667</v>
@@ -6366,7 +6366,7 @@
         <v>34.37624166666667</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4125149000000001</v>
+        <v>0.4125149</v>
       </c>
       <c r="L61" t="n">
         <v>241.561657116667</v>
@@ -8695,10 +8695,10 @@
         <v>56.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>56.03720000000001</v>
+        <v>56.0372</v>
       </c>
       <c r="N19" t="n">
-        <v>56.03720000000001</v>
+        <v>56.0372</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -11638,7 +11638,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -23712,7 +23712,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>950.0000000000001</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -23732,7 +23732,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -23812,7 +23812,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>505.2292200000001</v>
+        <v>505.22922</v>
       </c>
     </row>
     <row r="19">

--- a/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>25 / 0 / 3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -774,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +933,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -807,7 +951,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -822,7 +966,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -839,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +998,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -871,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -886,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -903,7 +1047,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +1062,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -935,7 +1079,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,7 +1094,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -967,7 +1111,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -982,7 +1126,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -999,7 +1143,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,7 +1158,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1046,7 +1190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1207,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1078,7 +1222,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1239,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1271,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1303,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1318,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1335,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1206,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1367,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1238,7 +1382,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,7 +1414,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1302,7 +1446,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1478,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1495,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1366,7 +1510,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1398,7 +1542,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10119,7 +10263,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stock after inflow 120.252 t exceeds ZBO modernization capacity 120.0 t within 2038-09 (before withdrawals)</t>
+          <t>запас после поступления 120.252 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-09 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10161,7 +10305,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stock after inflow 129.556 t exceeds ZBO modernization capacity 120.0 t within 2038-10 (before withdrawals)</t>
+          <t>запас после поступления 129.556 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-10 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10203,7 +10347,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stock after inflow 138.860 t exceeds ZBO modernization capacity 120.0 t within 2038-11 (before withdrawals)</t>
+          <t>запас после поступления 138.860 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-11 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10245,7 +10389,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>end-of-month stock 127.330 t exceeds ZBO modernization capacity 120.0 t in 2038-12</t>
+          <t>запас на конец месяца 127.330 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10287,7 +10431,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>end-of-month stock 134.627 t exceeds ZBO modernization capacity 120.0 t in 2039-01</t>
+          <t>запас на конец месяца 134.627 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10329,7 +10473,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>end-of-month stock 141.924 t exceeds ZBO modernization capacity 120.0 t in 2039-02</t>
+          <t>запас на конец месяца 141.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -10371,7 +10515,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>end-of-month stock 149.221 t exceeds ZBO modernization capacity 120.0 t in 2039-03</t>
+          <t>запас на конец месяца 149.221 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -10413,7 +10557,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>end-of-month stock 156.519 t exceeds ZBO modernization capacity 120.0 t in 2039-04</t>
+          <t>запас на конец месяца 156.519 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -10455,7 +10599,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>end-of-month stock 163.816 t exceeds ZBO modernization capacity 120.0 t in 2039-05</t>
+          <t>запас на конец месяца 163.816 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -10497,7 +10641,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>end-of-month stock 171.113 t exceeds ZBO modernization capacity 120.0 t in 2039-06</t>
+          <t>запас на конец месяца 171.113 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -10539,7 +10683,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>end-of-month stock 178.410 t exceeds ZBO modernization capacity 120.0 t in 2039-07</t>
+          <t>запас на конец месяца 178.410 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -10581,7 +10725,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>end-of-month stock 185.707 t exceeds ZBO modernization capacity 120.0 t in 2039-08</t>
+          <t>запас на конец месяца 185.707 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -10623,7 +10767,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>end-of-month stock 193.004 t exceeds ZBO modernization capacity 120.0 t in 2039-09</t>
+          <t>запас на конец месяца 193.004 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -10665,7 +10809,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>end-of-month stock 200.301 t exceeds ZBO modernization capacity 120.0 t in 2039-10</t>
+          <t>запас на конец месяца 200.301 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -10707,7 +10851,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>end-of-month stock 207.598 t exceeds ZBO modernization capacity 120.0 t in 2039-11</t>
+          <t>запас на конец месяца 207.598 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -10749,7 +10893,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>end-of-month stock 214.895 t exceeds ZBO modernization capacity 120.0 t in 2039-12</t>
+          <t>запас на конец месяца 214.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -10791,7 +10935,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>end-of-month stock 216.975 t exceeds ZBO modernization capacity 120.0 t in 2040-01</t>
+          <t>запас на конец месяца 216.975 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -10833,7 +10977,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>end-of-month stock 219.055 t exceeds ZBO modernization capacity 120.0 t in 2040-02</t>
+          <t>запас на конец месяца 219.055 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -10875,7 +11019,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>end-of-month stock 221.135 t exceeds ZBO modernization capacity 120.0 t in 2040-03</t>
+          <t>запас на конец месяца 221.135 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -10917,7 +11061,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>end-of-month stock 223.215 t exceeds ZBO modernization capacity 120.0 t in 2040-04</t>
+          <t>запас на конец месяца 223.215 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -10959,7 +11103,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>end-of-month stock 225.295 t exceeds ZBO modernization capacity 120.0 t in 2040-05</t>
+          <t>запас на конец месяца 225.295 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -11001,7 +11145,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>end-of-month stock 227.375 t exceeds ZBO modernization capacity 120.0 t in 2040-06</t>
+          <t>запас на конец месяца 227.375 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -11043,7 +11187,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>end-of-month stock 229.455 t exceeds ZBO modernization capacity 120.0 t in 2040-07</t>
+          <t>запас на конец месяца 229.455 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -11085,7 +11229,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>end-of-month stock 231.535 t exceeds ZBO modernization capacity 120.0 t in 2040-08</t>
+          <t>запас на конец месяца 231.535 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -11127,7 +11271,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>end-of-month stock 233.615 t exceeds ZBO modernization capacity 120.0 t in 2040-09</t>
+          <t>запас на конец месяца 233.615 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -11169,7 +11313,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>end-of-month stock 235.695 t exceeds ZBO modernization capacity 120.0 t in 2040-10</t>
+          <t>запас на конец месяца 235.695 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -11211,7 +11355,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>end-of-month stock 237.775 t exceeds ZBO modernization capacity 120.0 t in 2040-11</t>
+          <t>запас на конец месяца 237.775 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -11253,7 +11397,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>end-of-month stock 239.855 t exceeds ZBO modernization capacity 120.0 t in 2040-12</t>
+          <t>запас на конец месяца 239.855 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -12650,7 +12794,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12663,7 +12807,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12843,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12712,7 +12856,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12748,7 +12892,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12761,7 +12905,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12797,7 +12941,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12810,7 +12954,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12990,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12859,7 +13003,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12895,7 +13039,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12908,7 +13052,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -15019,7 +15163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M155"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15088,6 +15232,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15143,6 +15292,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15198,6 +15352,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15253,6 +15412,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15308,6 +15472,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15363,6 +15532,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15418,6 +15592,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15473,6 +15652,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15528,6 +15712,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15583,6 +15772,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15638,6 +15832,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15693,6 +15892,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15748,6 +15952,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15803,6 +16012,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15858,6 +16072,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15913,6 +16132,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15968,6 +16192,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16023,6 +16252,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16078,6 +16312,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16133,6 +16372,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16188,6 +16432,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16243,6 +16492,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16298,6 +16552,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16353,6 +16612,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16408,6 +16672,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16463,6 +16732,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16518,6 +16792,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16573,6 +16852,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16628,6 +16912,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16683,6 +16972,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16738,6 +17032,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16793,6 +17092,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16848,6 +17152,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16903,6 +17212,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16958,6 +17272,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17013,6 +17332,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17068,6 +17392,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17123,6 +17452,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17178,6 +17512,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17233,6 +17572,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17288,6 +17632,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17343,6 +17692,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17398,6 +17752,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17453,6 +17812,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17508,6 +17872,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17563,6 +17932,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17618,6 +17992,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17673,6 +18052,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17728,6 +18112,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17783,6 +18172,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17838,6 +18232,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17893,6 +18292,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17948,6 +18352,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18003,6 +18412,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18058,6 +18472,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -18113,6 +18532,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18168,6 +18592,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18223,6 +18652,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18278,6 +18712,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18333,6 +18772,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18388,6 +18832,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -18443,6 +18892,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -18498,6 +18952,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -18553,6 +19012,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18608,6 +19072,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18663,6 +19132,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18718,6 +19192,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18773,6 +19252,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18828,6 +19312,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18883,6 +19372,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18938,6 +19432,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18993,6 +19492,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -19048,6 +19552,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -19103,6 +19612,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -19158,6 +19672,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -19213,6 +19732,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -19268,6 +19792,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -19323,6 +19852,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -19378,6 +19912,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -19433,6 +19972,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19488,6 +20032,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19543,6 +20092,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -19598,6 +20152,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19653,6 +20212,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19708,6 +20272,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19763,6 +20332,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19818,6 +20392,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19873,6 +20452,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19928,6 +20512,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19983,6 +20572,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -20038,6 +20632,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -20093,6 +20692,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -20148,6 +20752,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -20203,6 +20812,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -20258,6 +20872,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -20313,6 +20932,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -20368,6 +20992,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -20423,6 +21052,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -20478,6 +21112,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -20533,6 +21172,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -20588,6 +21232,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -20643,6 +21292,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -20698,6 +21352,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -20753,6 +21412,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20808,6 +21472,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20863,6 +21532,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20918,6 +21592,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20973,6 +21652,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -21028,6 +21712,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -21083,6 +21772,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -21138,6 +21832,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -21193,6 +21892,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -21248,6 +21952,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -21303,6 +22012,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -21358,6 +22072,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -21413,6 +22132,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -21468,6 +22192,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -21523,6 +22252,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -21578,6 +22312,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -21633,6 +22372,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -21688,6 +22432,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -21743,6 +22492,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -21798,6 +22552,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -21853,6 +22612,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -21908,6 +22672,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21963,6 +22732,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -22018,6 +22792,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -22073,6 +22852,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -22128,6 +22912,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -22183,6 +22972,11 @@
       <c r="M130" t="b">
         <v>1</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -22238,6 +23032,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -22293,6 +23092,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -22348,6 +23152,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -22403,6 +23212,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -22458,6 +23272,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -22513,6 +23332,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22568,6 +23392,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -22623,6 +23452,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -22678,6 +23512,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -22733,6 +23572,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22788,6 +23632,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22843,6 +23692,11 @@
       <c r="M142" t="b">
         <v>1</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -22898,6 +23752,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -22953,6 +23812,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -23008,6 +23872,11 @@
       <c r="M145" t="b">
         <v>1</v>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -23063,6 +23932,11 @@
       <c r="M146" t="b">
         <v>1</v>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -23118,6 +23992,11 @@
       <c r="M147" t="b">
         <v>1</v>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -23173,6 +24052,11 @@
       <c r="M148" t="b">
         <v>1</v>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -23228,6 +24112,11 @@
       <c r="M149" t="b">
         <v>1</v>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -23283,6 +24172,11 @@
       <c r="M150" t="b">
         <v>1</v>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -23338,6 +24232,11 @@
       <c r="M151" t="b">
         <v>1</v>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -23393,6 +24292,11 @@
       <c r="M152" t="b">
         <v>1</v>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -23448,6 +24352,11 @@
       <c r="M153" t="b">
         <v>1</v>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -23503,6 +24412,11 @@
       <c r="M154" t="b">
         <v>1</v>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -23557,6 +24471,11 @@
       </c>
       <c r="M155" t="b">
         <v>1</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -12783,18 +12816,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12807,7 +12840,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12832,18 +12865,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12856,7 +12889,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12881,18 +12914,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12905,7 +12938,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12930,18 +12963,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12954,7 +12987,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12979,18 +13012,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -13003,7 +13036,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13028,18 +13061,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -13052,7 +13085,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13110,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -13101,7 +13134,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13345,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -13336,7 +13369,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13547,11 +13580,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>35.44551565000008</v>
+        <v>27.71964825000006</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -13571,7 +13604,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13913,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -13904,7 +13937,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14311,7 +14344,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -14335,7 +14368,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14742,7 +14775,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -14766,7 +14799,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>2.6922</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>8.4057</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>15.37725</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>16.5</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9970,6 +10065,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24621,7 +24742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25059,11 +25180,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -25079,11 +25200,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>239.8549904500003</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -25099,11 +25220,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>239.8549904500003</v>
       </c>
     </row>
     <row r="25">
@@ -25119,11 +25240,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -25139,11 +25260,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -25159,11 +25280,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -25179,11 +25300,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>77</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -25199,10 +25320,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>74</v>
       </c>
     </row>

--- a/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
+++ b/results/stress/P3_isru_zbo_adapted_BASE/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25 / 0 / 3</t>
+          <t>53 / 0 / 0</t>
         </is>
       </c>
     </row>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>1.426968181250004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.97403137500007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>1.469915583750004</v>
       </c>
       <c r="U27" t="n">
+        <v>40.68982141666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>1.512862986250004</v>
       </c>
       <c r="U28" t="n">
+        <v>41.4056114583334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>1.555810388750004</v>
       </c>
       <c r="U29" t="n">
+        <v>42.12140150000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>1.598757791250004</v>
       </c>
       <c r="U30" t="n">
+        <v>42.83719154166673</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>1.641705193750004</v>
       </c>
       <c r="U31" t="n">
+        <v>43.5529815833334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>1.701808232000004</v>
       </c>
       <c r="U32" t="n">
+        <v>44.84062615000006</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>1.779066906000004</v>
       </c>
       <c r="U33" t="n">
+        <v>46.12827071666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>1.856325580000004</v>
       </c>
       <c r="U34" t="n">
+        <v>47.4159152833334</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>1.933584254000004</v>
       </c>
       <c r="U35" t="n">
+        <v>48.70355985000008</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>2.010842928000005</v>
       </c>
       <c r="U36" t="n">
+        <v>49.99120441666675</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>2.088101602000005</v>
       </c>
       <c r="U37" t="n">
+        <v>51.27884898333342</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>2.109442823000005</v>
       </c>
       <c r="U38" t="n">
+        <v>55.70257845000008</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>2.074866591000005</v>
       </c>
       <c r="U39" t="n">
+        <v>55.12630791666675</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>2.336690359000005</v>
       </c>
       <c r="U40" t="n">
+        <v>64.43003738333341</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>2.894914127000006</v>
       </c>
       <c r="U41" t="n">
+        <v>73.73376685000009</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>3.453137895000007</v>
       </c>
       <c r="U42" t="n">
+        <v>83.03749631666678</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>4.011361663000008</v>
       </c>
       <c r="U43" t="n">
+        <v>92.34122578333346</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>4.569585431000009</v>
       </c>
       <c r="U44" t="n">
+        <v>101.6449552500001</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>5.127809199000009</v>
       </c>
       <c r="U45" t="n">
+        <v>110.9486847166668</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>5.686032967000011</v>
       </c>
       <c r="U46" t="n">
+        <v>120.2524141833335</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>6.244256735000011</v>
       </c>
       <c r="U47" t="n">
+        <v>129.5561436500002</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>6.802480503000012</v>
       </c>
       <c r="U48" t="n">
+        <v>138.8598731166669</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>7.360704271000013</v>
       </c>
       <c r="U49" t="n">
+        <v>148.1636025833336</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>7.858727958000014</v>
       </c>
       <c r="U50" t="n">
+        <v>161.2939960166669</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>8.296551564000016</v>
       </c>
       <c r="U51" t="n">
+        <v>168.5910561166669</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>8.734375170000016</v>
       </c>
       <c r="U52" t="n">
+        <v>175.8881162166669</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>9.172198776000016</v>
       </c>
       <c r="U53" t="n">
+        <v>183.1851763166669</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>9.610022382000016</v>
       </c>
       <c r="U54" t="n">
+        <v>190.482236416667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>10.04784598800002</v>
       </c>
       <c r="U55" t="n">
+        <v>197.779296516667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>10.48566959400002</v>
       </c>
       <c r="U56" t="n">
+        <v>205.076356616667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>10.92349320000002</v>
       </c>
       <c r="U57" t="n">
+        <v>212.373416716667</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>11.36131680600002</v>
       </c>
       <c r="U58" t="n">
+        <v>219.670476816667</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>11.79914041200002</v>
       </c>
       <c r="U59" t="n">
+        <v>226.967536916667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>12.23696401800002</v>
       </c>
       <c r="U60" t="n">
+        <v>234.264597016667</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>12.67478762400002</v>
       </c>
       <c r="U61" t="n">
+        <v>241.561657116667</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>12.95609942700002</v>
       </c>
       <c r="U62" t="n">
+        <v>249.4749904500003</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>13.08089942700002</v>
       </c>
       <c r="U63" t="n">
+        <v>251.5549904500004</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>13.20569942700003</v>
       </c>
       <c r="U64" t="n">
+        <v>253.6349904500004</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>13.33049942700002</v>
       </c>
       <c r="U65" t="n">
+        <v>255.7149904500004</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>13.45529942700002</v>
       </c>
       <c r="U66" t="n">
+        <v>257.7949904500004</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>13.58009942700002</v>
       </c>
       <c r="U67" t="n">
+        <v>259.8749904500004</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>13.70489942700002</v>
       </c>
       <c r="U68" t="n">
+        <v>261.9549904500004</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>13.82969942700002</v>
       </c>
       <c r="U69" t="n">
+        <v>264.0349904500004</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>13.95449942700002</v>
       </c>
       <c r="U70" t="n">
+        <v>266.1149904500003</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>14.07929942700002</v>
       </c>
       <c r="U71" t="n">
+        <v>268.1949904500003</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>14.20409942700002</v>
       </c>
       <c r="U72" t="n">
+        <v>270.2749904500003</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>14.32889942700002</v>
       </c>
       <c r="U73" t="n">
+        <v>272.3549904500003</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10433,7 +11020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10511,12 +11098,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>запас после поступления 120.252 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-09 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 120.252 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-09 (поставка одной партией в начале месяца; запас на начало 90.115 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10532,7 +11119,7 @@
         <v>120</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2524141833335136</v>
+        <v>0.2524141833334994</v>
       </c>
     </row>
     <row r="3">
@@ -10553,12 +11140,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>запас после поступления 129.556 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-10 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 129.556 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-10 (поставка одной партией в начале месяца; запас на начало 99.419 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10595,12 +11182,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>запас после поступления 138.860 т превышает ёмкость хранилища ZBO modernization 120.0 т внутри 2038-11 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 138.860 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-11 (поставка одной партией в начале месяца; запас на начало 108.723 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10674,7 +11261,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10684,23 +11271,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>запас на конец месяца 134.627 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
+          <t>пик запаса внутри месяца 148.164 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2038-12 (поставка одной партией в начале месяца; запас на начало 118.027 т, нетто-поступление 30.137 т, выдача 20.833 т)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>134.6273293500003</v>
+        <v>148.1636025833336</v>
       </c>
       <c r="J6" t="n">
         <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>14.62732935000025</v>
+        <v>28.16360258333356</v>
       </c>
     </row>
     <row r="7">
@@ -10726,23 +11313,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>запас на конец месяца 141.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
+          <t>запас на конец месяца 134.627 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2039</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>141.9243894500003</v>
+        <v>134.6273293500003</v>
       </c>
       <c r="J7" t="n">
         <v>120</v>
       </c>
       <c r="K7" t="n">
-        <v>21.92438945000026</v>
+        <v>14.62732935000025</v>
       </c>
     </row>
     <row r="8">
@@ -10758,7 +11345,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10768,23 +11355,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>запас на конец месяца 149.221 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
+          <t>пик запаса внутри месяца 161.294 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-01 (поставка одной партией в начале месяца; запас на начало 127.330 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2039</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>149.2214495500003</v>
+        <v>161.2939960166669</v>
       </c>
       <c r="J8" t="n">
         <v>120</v>
       </c>
       <c r="K8" t="n">
-        <v>29.22144955000027</v>
+        <v>41.29399601666688</v>
       </c>
     </row>
     <row r="9">
@@ -10810,23 +11397,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>запас на конец месяца 156.519 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
+          <t>запас на конец месяца 141.924 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2039</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>156.5185096500003</v>
+        <v>141.9243894500003</v>
       </c>
       <c r="J9" t="n">
         <v>120</v>
       </c>
       <c r="K9" t="n">
-        <v>36.51850965000028</v>
+        <v>21.92438945000026</v>
       </c>
     </row>
     <row r="10">
@@ -10842,7 +11429,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10852,23 +11439,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>запас на конец месяца 163.816 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
+          <t>пик запаса внутри месяца 168.591 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-02 (поставка одной партией в начале месяца; запас на начало 134.627 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2039</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>163.8155697500003</v>
+        <v>168.5910561166669</v>
       </c>
       <c r="J10" t="n">
         <v>120</v>
       </c>
       <c r="K10" t="n">
-        <v>43.81556975000029</v>
+        <v>48.59105611666692</v>
       </c>
     </row>
     <row r="11">
@@ -10894,23 +11481,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>запас на конец месяца 171.113 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
+          <t>запас на конец месяца 149.221 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2039</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>171.1126298500003</v>
+        <v>149.2214495500003</v>
       </c>
       <c r="J11" t="n">
         <v>120</v>
       </c>
       <c r="K11" t="n">
-        <v>51.1126298500003</v>
+        <v>29.22144955000027</v>
       </c>
     </row>
     <row r="12">
@@ -10926,7 +11513,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10936,23 +11523,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>запас на конец месяца 178.410 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
+          <t>пик запаса внутри месяца 175.888 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-03 (поставка одной партией в начале месяца; запас на начало 141.924 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2039</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>178.4096899500003</v>
+        <v>175.8881162166669</v>
       </c>
       <c r="J12" t="n">
         <v>120</v>
       </c>
       <c r="K12" t="n">
-        <v>58.40968995000031</v>
+        <v>55.88811621666693</v>
       </c>
     </row>
     <row r="13">
@@ -10978,23 +11565,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>запас на конец месяца 185.707 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
+          <t>запас на конец месяца 156.519 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2039</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>185.7067500500003</v>
+        <v>156.5185096500003</v>
       </c>
       <c r="J13" t="n">
         <v>120</v>
       </c>
       <c r="K13" t="n">
-        <v>65.70675005000032</v>
+        <v>36.51850965000028</v>
       </c>
     </row>
     <row r="14">
@@ -11010,7 +11597,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11020,23 +11607,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>запас на конец месяца 193.004 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
+          <t>пик запаса внутри месяца 183.185 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-04 (поставка одной партией в начале месяца; запас на начало 149.221 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2039</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>193.0038101500003</v>
+        <v>183.1851763166669</v>
       </c>
       <c r="J14" t="n">
         <v>120</v>
       </c>
       <c r="K14" t="n">
-        <v>73.00381015000033</v>
+        <v>63.18517631666694</v>
       </c>
     </row>
     <row r="15">
@@ -11062,23 +11649,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>запас на конец месяца 200.301 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
+          <t>запас на конец месяца 163.816 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2039</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>200.3008702500003</v>
+        <v>163.8155697500003</v>
       </c>
       <c r="J15" t="n">
         <v>120</v>
       </c>
       <c r="K15" t="n">
-        <v>80.30087025000034</v>
+        <v>43.81556975000029</v>
       </c>
     </row>
     <row r="16">
@@ -11094,7 +11681,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11104,23 +11691,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>запас на конец месяца 207.598 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
+          <t>пик запаса внутри месяца 190.482 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-05 (поставка одной партией в начале месяца; запас на начало 156.519 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2039</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>207.5979303500004</v>
+        <v>190.482236416667</v>
       </c>
       <c r="J16" t="n">
         <v>120</v>
       </c>
       <c r="K16" t="n">
-        <v>87.59793035000035</v>
+        <v>70.48223641666695</v>
       </c>
     </row>
     <row r="17">
@@ -11146,23 +11733,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>запас на конец месяца 214.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
+          <t>запас на конец месяца 171.113 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2039</v>
       </c>
       <c r="G17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>214.8949904500004</v>
+        <v>171.1126298500003</v>
       </c>
       <c r="J17" t="n">
         <v>120</v>
       </c>
       <c r="K17" t="n">
-        <v>94.89499045000036</v>
+        <v>51.1126298500003</v>
       </c>
     </row>
     <row r="18">
@@ -11178,7 +11765,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11188,23 +11775,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>запас на конец месяца 216.975 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
+          <t>пик запаса внутри месяца 197.779 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-06 (поставка одной партией в начале месяца; запас на начало 163.816 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>216.9749904500004</v>
+        <v>197.779296516667</v>
       </c>
       <c r="J18" t="n">
         <v>120</v>
       </c>
       <c r="K18" t="n">
-        <v>96.97499045000038</v>
+        <v>77.77929651666696</v>
       </c>
     </row>
     <row r="19">
@@ -11230,23 +11817,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>запас на конец месяца 219.055 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
+          <t>запас на конец месяца 178.410 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>219.0549904500004</v>
+        <v>178.4096899500003</v>
       </c>
       <c r="J19" t="n">
         <v>120</v>
       </c>
       <c r="K19" t="n">
-        <v>99.05499045000039</v>
+        <v>58.40968995000031</v>
       </c>
     </row>
     <row r="20">
@@ -11262,7 +11849,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11272,23 +11859,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>запас на конец месяца 221.135 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
+          <t>пик запаса внутри месяца 205.076 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-07 (поставка одной партией в начале месяца; запас на начало 171.113 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>221.1349904500004</v>
+        <v>205.076356616667</v>
       </c>
       <c r="J20" t="n">
         <v>120</v>
       </c>
       <c r="K20" t="n">
-        <v>101.1349904500004</v>
+        <v>85.07635661666697</v>
       </c>
     </row>
     <row r="21">
@@ -11314,23 +11901,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>запас на конец месяца 223.215 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
+          <t>запас на конец месяца 185.707 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>223.2149904500004</v>
+        <v>185.7067500500003</v>
       </c>
       <c r="J21" t="n">
         <v>120</v>
       </c>
       <c r="K21" t="n">
-        <v>103.2149904500004</v>
+        <v>65.70675005000032</v>
       </c>
     </row>
     <row r="22">
@@ -11346,7 +11933,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -11356,23 +11943,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>запас на конец месяца 225.295 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
+          <t>пик запаса внутри месяца 212.373 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-08 (поставка одной партией в начале месяца; запас на начало 178.410 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>225.2949904500004</v>
+        <v>212.373416716667</v>
       </c>
       <c r="J22" t="n">
         <v>120</v>
       </c>
       <c r="K22" t="n">
-        <v>105.2949904500004</v>
+        <v>92.37341671666698</v>
       </c>
     </row>
     <row r="23">
@@ -11398,23 +11985,23 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>запас на конец месяца 227.375 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
+          <t>запас на конец месяца 193.004 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>227.3749904500004</v>
+        <v>193.0038101500003</v>
       </c>
       <c r="J23" t="n">
         <v>120</v>
       </c>
       <c r="K23" t="n">
-        <v>107.3749904500004</v>
+        <v>73.00381015000033</v>
       </c>
     </row>
     <row r="24">
@@ -11430,7 +12017,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11440,23 +12027,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>запас на конец месяца 229.455 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
+          <t>пик запаса внутри месяца 219.670 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-09 (поставка одной партией в начале месяца; запас на начало 185.707 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>229.4549904500004</v>
+        <v>219.670476816667</v>
       </c>
       <c r="J24" t="n">
         <v>120</v>
       </c>
       <c r="K24" t="n">
-        <v>109.4549904500004</v>
+        <v>99.67047681666699</v>
       </c>
     </row>
     <row r="25">
@@ -11482,23 +12069,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>запас на конец месяца 231.535 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
+          <t>запас на конец месяца 200.301 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>231.5349904500004</v>
+        <v>200.3008702500003</v>
       </c>
       <c r="J25" t="n">
         <v>120</v>
       </c>
       <c r="K25" t="n">
-        <v>111.5349904500004</v>
+        <v>80.30087025000034</v>
       </c>
     </row>
     <row r="26">
@@ -11514,7 +12101,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11524,23 +12111,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>запас на конец месяца 233.615 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
+          <t>пик запаса внутри месяца 226.968 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-10 (поставка одной партией в начале месяца; запас на начало 193.004 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>233.6149904500003</v>
+        <v>226.967536916667</v>
       </c>
       <c r="J26" t="n">
         <v>120</v>
       </c>
       <c r="K26" t="n">
-        <v>113.6149904500003</v>
+        <v>106.967536916667</v>
       </c>
     </row>
     <row r="27">
@@ -11566,23 +12153,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>запас на конец месяца 235.695 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
+          <t>запас на конец месяца 207.598 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>235.6949904500003</v>
+        <v>207.5979303500004</v>
       </c>
       <c r="J27" t="n">
         <v>120</v>
       </c>
       <c r="K27" t="n">
-        <v>115.6949904500003</v>
+        <v>87.59793035000035</v>
       </c>
     </row>
     <row r="28">
@@ -11598,7 +12185,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11608,23 +12195,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>запас на конец месяца 237.775 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
+          <t>пик запаса внутри месяца 234.265 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-11 (поставка одной партией в начале месяца; запас на начало 200.301 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G28" t="n">
         <v>11</v>
       </c>
       <c r="I28" t="n">
-        <v>237.7749904500003</v>
+        <v>234.264597016667</v>
       </c>
       <c r="J28" t="n">
         <v>120</v>
       </c>
       <c r="K28" t="n">
-        <v>117.7749904500003</v>
+        <v>114.264597016667</v>
       </c>
     </row>
     <row r="29">
@@ -11650,23 +12237,1073 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>запас на конец месяца 239.855 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
+          <t>запас на конец месяца 214.895 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="G29" t="n">
         <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>239.8549904500003</v>
+        <v>214.8949904500004</v>
       </c>
       <c r="J29" t="n">
         <v>120</v>
       </c>
       <c r="K29" t="n">
+        <v>94.89499045000036</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 241.562 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2039-12 (поставка одной партией в начале месяца; запас на начало 207.598 т, нетто-поступление 33.964 т, выдача 26.667 т)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2039</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>241.561657116667</v>
+      </c>
+      <c r="J30" t="n">
+        <v>120</v>
+      </c>
+      <c r="K30" t="n">
+        <v>121.561657116667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 216.975 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>216.9749904500004</v>
+      </c>
+      <c r="J31" t="n">
+        <v>120</v>
+      </c>
+      <c r="K31" t="n">
+        <v>96.97499045000038</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 249.475 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-01 (поставка одной партией в начале месяца; запас на начало 214.895 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>249.4749904500003</v>
+      </c>
+      <c r="J32" t="n">
+        <v>120</v>
+      </c>
+      <c r="K32" t="n">
+        <v>129.4749904500003</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 219.055 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>219.0549904500004</v>
+      </c>
+      <c r="J33" t="n">
+        <v>120</v>
+      </c>
+      <c r="K33" t="n">
+        <v>99.05499045000039</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 251.555 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-02 (поставка одной партией в начале месяца; запас на начало 216.975 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>251.5549904500004</v>
+      </c>
+      <c r="J34" t="n">
+        <v>120</v>
+      </c>
+      <c r="K34" t="n">
+        <v>131.5549904500004</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 221.135 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>221.1349904500004</v>
+      </c>
+      <c r="J35" t="n">
+        <v>120</v>
+      </c>
+      <c r="K35" t="n">
+        <v>101.1349904500004</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 253.635 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-03 (поставка одной партией в начале месяца; запас на начало 219.055 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>253.6349904500004</v>
+      </c>
+      <c r="J36" t="n">
+        <v>120</v>
+      </c>
+      <c r="K36" t="n">
+        <v>133.6349904500004</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 223.215 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>223.2149904500004</v>
+      </c>
+      <c r="J37" t="n">
+        <v>120</v>
+      </c>
+      <c r="K37" t="n">
+        <v>103.2149904500004</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 255.715 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-04 (поставка одной партией в начале месяца; запас на начало 221.135 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>255.7149904500004</v>
+      </c>
+      <c r="J38" t="n">
+        <v>120</v>
+      </c>
+      <c r="K38" t="n">
+        <v>135.7149904500004</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 225.295 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>225.2949904500004</v>
+      </c>
+      <c r="J39" t="n">
+        <v>120</v>
+      </c>
+      <c r="K39" t="n">
+        <v>105.2949904500004</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 257.795 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-05 (поставка одной партией в начале месяца; запас на начало 223.215 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>257.7949904500004</v>
+      </c>
+      <c r="J40" t="n">
+        <v>120</v>
+      </c>
+      <c r="K40" t="n">
+        <v>137.7949904500004</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 227.375 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>227.3749904500004</v>
+      </c>
+      <c r="J41" t="n">
+        <v>120</v>
+      </c>
+      <c r="K41" t="n">
+        <v>107.3749904500004</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 259.875 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-06 (поставка одной партией в начале месяца; запас на начало 225.295 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>259.8749904500004</v>
+      </c>
+      <c r="J42" t="n">
+        <v>120</v>
+      </c>
+      <c r="K42" t="n">
+        <v>139.8749904500004</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 229.455 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>229.4549904500004</v>
+      </c>
+      <c r="J43" t="n">
+        <v>120</v>
+      </c>
+      <c r="K43" t="n">
+        <v>109.4549904500004</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 261.955 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-07 (поставка одной партией в начале месяца; запас на начало 227.375 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>261.9549904500004</v>
+      </c>
+      <c r="J44" t="n">
+        <v>120</v>
+      </c>
+      <c r="K44" t="n">
+        <v>141.9549904500004</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 231.535 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" t="n">
+        <v>231.5349904500004</v>
+      </c>
+      <c r="J45" t="n">
+        <v>120</v>
+      </c>
+      <c r="K45" t="n">
+        <v>111.5349904500004</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 264.035 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-08 (поставка одной партией в начале месяца; запас на начало 229.455 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>264.0349904500004</v>
+      </c>
+      <c r="J46" t="n">
+        <v>120</v>
+      </c>
+      <c r="K46" t="n">
+        <v>144.0349904500004</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 233.615 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G47" t="n">
+        <v>9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>233.6149904500003</v>
+      </c>
+      <c r="J47" t="n">
+        <v>120</v>
+      </c>
+      <c r="K47" t="n">
+        <v>113.6149904500003</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 266.115 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-09 (поставка одной партией в начале месяца; запас на начало 231.535 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="I48" t="n">
+        <v>266.1149904500003</v>
+      </c>
+      <c r="J48" t="n">
+        <v>120</v>
+      </c>
+      <c r="K48" t="n">
+        <v>146.1149904500003</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 235.695 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I49" t="n">
+        <v>235.6949904500003</v>
+      </c>
+      <c r="J49" t="n">
+        <v>120</v>
+      </c>
+      <c r="K49" t="n">
+        <v>115.6949904500003</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 268.195 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-10 (поставка одной партией в начале месяца; запас на начало 233.615 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="n">
+        <v>268.1949904500003</v>
+      </c>
+      <c r="J50" t="n">
+        <v>120</v>
+      </c>
+      <c r="K50" t="n">
+        <v>148.1949904500003</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 237.775 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G51" t="n">
+        <v>11</v>
+      </c>
+      <c r="I51" t="n">
+        <v>237.7749904500003</v>
+      </c>
+      <c r="J51" t="n">
+        <v>120</v>
+      </c>
+      <c r="K51" t="n">
+        <v>117.7749904500003</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 270.275 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-11 (поставка одной партией в начале месяца; запас на начало 235.695 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11</v>
+      </c>
+      <c r="I52" t="n">
+        <v>270.2749904500003</v>
+      </c>
+      <c r="J52" t="n">
+        <v>120</v>
+      </c>
+      <c r="K52" t="n">
+        <v>150.2749904500003</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>STORAGE_OVERFLOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>запас на конец месяца 239.855 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G53" t="n">
+        <v>12</v>
+      </c>
+      <c r="I53" t="n">
+        <v>239.8549904500003</v>
+      </c>
+      <c r="J53" t="n">
+        <v>120</v>
+      </c>
+      <c r="K53" t="n">
         <v>119.8549904500003</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INTRA_MONTH_PEAK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>пик запаса внутри месяца 272.355 т превышает ёмкость хранилища ZBO modernization 120.0 т в 2040-12 (поставка одной партией в начале месяца; запас на начало 237.775 т, нетто-поступление 34.580 т, выдача 32.500 т)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G54" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>272.3549904500003</v>
+      </c>
+      <c r="J54" t="n">
+        <v>120</v>
+      </c>
+      <c r="K54" t="n">
+        <v>152.3549904500003</v>
       </c>
     </row>
   </sheetData>
@@ -11680,7 +13317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13371,7 +15008,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -13379,14 +15016,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -13403,7 +15040,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13420,7 +15057,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -13428,14 +15065,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -13469,7 +15106,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -13477,18 +15114,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -13498,7 +15136,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13513,7 +15155,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -13521,7 +15163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -13557,27 +15199,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -13587,11 +15228,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13606,7 +15243,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -13614,14 +15251,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -13638,7 +15275,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13655,7 +15292,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -13663,14 +15300,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -13687,7 +15324,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13704,7 +15341,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -13712,170 +15349,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>27.71964825000006</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13890,7 +15527,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -13898,14 +15535,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>27.71964825000006</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -13922,7 +15559,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13939,7 +15576,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -13947,14 +15584,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>17.948</v>
+        <v>43.5529815833334</v>
       </c>
       <c r="G48" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -13971,7 +15608,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13988,7 +15625,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -13996,14 +15633,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>17.9471</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>17.948</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -14020,7 +15657,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14037,7 +15674,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -14045,219 +15682,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>17.948</v>
+      </c>
+      <c r="G51" t="n">
+        <v>110</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>17.9471</v>
+      </c>
+      <c r="G52" t="n">
+        <v>17.948</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>127.3302692500002</v>
-      </c>
-      <c r="G52" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>190</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>190</v>
-      </c>
-      <c r="G54" t="n">
-        <v>190</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14272,7 +15909,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -14280,14 +15917,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>56.038</v>
+        <v>127.3302692500002</v>
       </c>
       <c r="G55" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -14295,7 +15932,7 @@
         </is>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -14304,7 +15941,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14321,7 +15958,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -14329,14 +15966,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>56.0372</v>
+        <v>148.1636025833336</v>
       </c>
       <c r="G56" t="n">
-        <v>56.038</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -14344,7 +15981,7 @@
         </is>
       </c>
       <c r="I56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -14353,7 +15990,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14378,14 +16015,14 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G57" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -14402,7 +16039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14427,14 +16064,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -14451,7 +16088,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14468,7 +16105,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -14476,268 +16113,268 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="G59" t="n">
+        <v>110</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>56.0372</v>
+      </c>
+      <c r="G60" t="n">
+        <v>56.038</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>120</v>
+      </c>
+      <c r="G61" t="n">
+        <v>120</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" t="n">
+        <v>100</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59">
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63">
         <f>=</f>
         <v/>
       </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D64" t="n">
         <v>2038</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60">
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64">
         <f>=</f>
         <v/>
       </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>214.8949904500004</v>
-      </c>
-      <c r="G61" t="n">
-        <v>120</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>190</v>
-      </c>
-      <c r="G62" t="n">
-        <v>190</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>190</v>
-      </c>
-      <c r="G63" t="n">
-        <v>190</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I63" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>102.515</v>
-      </c>
-      <c r="G64" t="n">
-        <v>110</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -14752,7 +16389,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -14760,14 +16397,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>102.5149</v>
+        <v>214.8949904500004</v>
       </c>
       <c r="G65" t="n">
-        <v>102.515</v>
+        <v>120</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -14775,7 +16412,7 @@
         </is>
       </c>
       <c r="I65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -14784,7 +16421,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14801,7 +16438,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -14809,11 +16446,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>120</v>
+        <v>241.561657116667</v>
       </c>
       <c r="G66" t="n">
         <v>120</v>
@@ -14824,7 +16461,7 @@
         </is>
       </c>
       <c r="I66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -14833,7 +16470,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14850,7 +16487,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -14858,14 +16495,14 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G67" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -14882,7 +16519,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14899,7 +16536,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -14907,317 +16544,317 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>190</v>
+      </c>
+      <c r="G68" t="n">
+        <v>190</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>102.515</v>
+      </c>
+      <c r="G69" t="n">
+        <v>110</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>102.5149</v>
+      </c>
+      <c r="G70" t="n">
+        <v>102.515</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>120</v>
+      </c>
+      <c r="G71" t="n">
+        <v>120</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>120</v>
+      </c>
+      <c r="G72" t="n">
+        <v>120</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68">
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73">
         <f>=</f>
         <v/>
       </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D74" t="n">
         <v>2039</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69">
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74">
         <f>=</f>
         <v/>
       </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>239.8549904500003</v>
-      </c>
-      <c r="G70" t="n">
-        <v>120</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>190</v>
-      </c>
-      <c r="G71" t="n">
-        <v>190</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>190</v>
-      </c>
-      <c r="G72" t="n">
-        <v>190</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>110</v>
-      </c>
-      <c r="G73" t="n">
-        <v>110</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>110</v>
-      </c>
-      <c r="G74" t="n">
-        <v>110</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -15232,7 +16869,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -15240,11 +16877,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>120</v>
+        <v>239.8549904500003</v>
       </c>
       <c r="G75" t="n">
         <v>120</v>
@@ -15255,7 +16892,7 @@
         </is>
       </c>
       <c r="I75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -15264,7 +16901,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -15281,7 +16918,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -15289,11 +16926,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>120</v>
+        <v>272.3549904500003</v>
       </c>
       <c r="G76" t="n">
         <v>120</v>
@@ -15304,7 +16941,7 @@
         </is>
       </c>
       <c r="I76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -15313,7 +16950,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -15330,7 +16967,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -15338,72 +16975,366 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>190</v>
+      </c>
+      <c r="G77" t="n">
+        <v>190</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>190</v>
+      </c>
+      <c r="G78" t="n">
+        <v>190</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>110</v>
+      </c>
+      <c r="G79" t="n">
+        <v>110</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>110</v>
+      </c>
+      <c r="G80" t="n">
+        <v>110</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>120</v>
+      </c>
+      <c r="G81" t="n">
+        <v>120</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>120</v>
+      </c>
+      <c r="G82" t="n">
+        <v>120</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77">
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83">
         <f>=</f>
         <v/>
       </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_adapted</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D84" t="n">
         <v>2040</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78">
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84">
         <f>=</f>
         <v/>
       </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24742,7 +26673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24784,7 +26715,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12599.578671007</v>
+        <v>12599.948536777</v>
       </c>
     </row>
     <row r="3">
@@ -24804,7 +26735,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10097.53518524926</v>
+        <v>10097.90505101926</v>
       </c>
     </row>
     <row r="4">
@@ -24944,7 +26875,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.064445087055397</v>
+        <v>9.064711177537411</v>
       </c>
     </row>
     <row r="11">
@@ -24964,7 +26895,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.264413802337595</v>
+        <v>7.264679892819609</v>
       </c>
     </row>
     <row r="12">
@@ -25124,7 +27055,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>385.4569910070006</v>
+        <v>385.8268567770007</v>
       </c>
     </row>
     <row r="20">
@@ -25240,11 +27171,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -25260,11 +27191,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -25280,11 +27211,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
@@ -25300,10 +27231,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25320,11 +27251,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -25340,11 +27271,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_adapted</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>74</v>
+      <c r="D32" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
